--- a/src/data/fixtures/market-insights/published-january-to-june-2026.xlsx
+++ b/src/data/fixtures/market-insights/published-january-to-june-2026.xlsx
@@ -330,7 +330,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">January </t>
+    <t>January</t>
   </si>
   <si>
     <t>February</t>
@@ -393,7 +393,7 @@
     <t>January 2026</t>
   </si>
   <si>
-    <t>Glass- re-melt</t>
+    <t>Glass re-melt</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -3361,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6489482D-E063-4D72-A5E0-6F684D9910F9}">
-  <dimension ref="A1:K281"/>
+  <dimension ref="A1:K277"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="17" customWidth="1"/>
@@ -4009,40 +4009,52 @@
       <c r="J48" s="52"/>
       <c r="K48" s="52"/>
     </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="18" t="s">
+    <row r="49" spans="1:11">
+      <c r="A49" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="51.4" customHeight="1">
-      <c r="A51" s="19" t="s">
+    <row r="50" spans="1:11" ht="51.4" customHeight="1">
+      <c r="A50" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B50" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C50" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D50" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E50" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F50" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G51" s="19" t="s">
+      <c r="G50" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H51" s="19" t="s">
+      <c r="H50" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -4054,7 +4066,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -4066,7 +4078,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -4078,7 +4090,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -4090,7 +4102,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -4100,9 +4112,9 @@
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" ht="14.65" thickBot="1">
       <c r="A57" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -4112,74 +4124,77 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A58" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-    </row>
-    <row r="59" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A59" s="22" t="s">
+    <row r="58" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A58" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-    </row>
-    <row r="60" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="61" spans="1:11">
-      <c r="A61" s="18" t="s">
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+    </row>
+    <row r="59" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="60" spans="1:11">
+      <c r="A60" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="49.15" customHeight="1">
-      <c r="A62" s="19" t="s">
+    <row r="61" spans="1:11" ht="49.15" customHeight="1">
+      <c r="A61" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B61" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C61" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D61" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E61" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F61" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="G61" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="H61" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="19" t="s">
+      <c r="I61" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J62" s="19" t="s">
+      <c r="J61" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K62" s="19" t="s">
+      <c r="K61" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -4194,12 +4209,12 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="E64" s="17"/>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
@@ -4209,12 +4224,12 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
-      <c r="E65" s="17"/>
+      <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
@@ -4224,7 +4239,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -4239,7 +4254,7 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -4252,9 +4267,9 @@
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" ht="14.65" thickBot="1">
       <c r="A68" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -4267,98 +4282,95 @@
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A69" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-    </row>
-    <row r="70" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A70" s="22" t="s">
+    <row r="69" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A69" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-    </row>
-    <row r="71" spans="1:11" s="34" customFormat="1" ht="14.65" thickTop="1">
-      <c r="A71" s="18"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-    </row>
-    <row r="72" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A72" s="52" t="s">
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+    </row>
+    <row r="70" spans="1:11" s="34" customFormat="1" ht="14.65" thickTop="1">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+    </row>
+    <row r="71" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A71" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="52"/>
-      <c r="K72" s="52"/>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="18" t="s">
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="48" customHeight="1">
-      <c r="A74" s="19" t="s">
+    <row r="73" spans="1:11" ht="48" customHeight="1">
+      <c r="A73" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B73" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C73" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D73" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E73" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F74" s="19" t="s">
+      <c r="F73" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G74" s="19" t="s">
+      <c r="G73" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H74" s="19" t="s">
+      <c r="H73" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -4370,7 +4382,7 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -4382,7 +4394,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -4394,7 +4406,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -4406,7 +4418,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -4416,9 +4428,9 @@
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" ht="14.65" thickBot="1">
       <c r="A80" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -4428,74 +4440,77 @@
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
     </row>
-    <row r="81" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A81" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-    </row>
-    <row r="82" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A82" s="22" t="s">
+    <row r="81" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A81" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="22"/>
-    </row>
-    <row r="83" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="84" spans="1:11">
-      <c r="A84" s="18" t="s">
+      <c r="B81" s="22"/>
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+    </row>
+    <row r="82" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="83" spans="1:11">
+      <c r="A83" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="50.65" customHeight="1">
-      <c r="A85" s="19" t="s">
+    <row r="84" spans="1:11" ht="50.65" customHeight="1">
+      <c r="A84" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B84" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C84" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D85" s="19" t="s">
+      <c r="D84" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E85" s="19" t="s">
+      <c r="E84" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F85" s="19" t="s">
+      <c r="F84" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G85" s="19" t="s">
+      <c r="G84" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H85" s="19" t="s">
+      <c r="H84" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I85" s="19" t="s">
+      <c r="I84" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J85" s="19" t="s">
+      <c r="J84" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K85" s="19" t="s">
+      <c r="K84" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -4510,7 +4525,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -4525,7 +4540,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -4540,7 +4555,7 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -4555,7 +4570,7 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -4568,9 +4583,9 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" ht="14.65" thickBot="1">
       <c r="A91" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -4583,98 +4598,95 @@
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A92" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-    </row>
-    <row r="93" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A93" s="22" t="s">
+    <row r="92" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A92" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B93" s="22"/>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22"/>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="22"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="22"/>
-    </row>
-    <row r="94" spans="1:11" ht="14.65" thickTop="1">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="18"/>
-      <c r="F94" s="18"/>
-      <c r="G94" s="18"/>
-      <c r="H94" s="18"/>
-      <c r="I94" s="18"/>
-      <c r="J94" s="18"/>
-      <c r="K94" s="18"/>
-    </row>
-    <row r="95" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A95" s="52" t="s">
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="22"/>
+      <c r="K92" s="22"/>
+    </row>
+    <row r="93" spans="1:11" ht="14.65" thickTop="1">
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="18"/>
+    </row>
+    <row r="94" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A94" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="18" t="s">
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="52"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="48" customHeight="1">
-      <c r="A97" s="19" t="s">
+    <row r="96" spans="1:11" ht="48" customHeight="1">
+      <c r="A96" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B97" s="19" t="s">
+      <c r="B96" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C96" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D97" s="19" t="s">
+      <c r="D96" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E96" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F97" s="19" t="s">
+      <c r="F96" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G97" s="19" t="s">
+      <c r="G96" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H97" s="19" t="s">
+      <c r="H96" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -4686,7 +4698,7 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -4698,7 +4710,7 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -4710,7 +4722,7 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -4722,7 +4734,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -4732,9 +4744,9 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" ht="14.65" thickBot="1">
       <c r="A103" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -4744,74 +4756,77 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A104" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-    </row>
-    <row r="105" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A105" s="22" t="s">
+    <row r="104" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A104" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B105" s="22"/>
-      <c r="C105" s="22"/>
-      <c r="D105" s="22"/>
-      <c r="E105" s="22"/>
-      <c r="F105" s="22"/>
-      <c r="G105" s="22"/>
-      <c r="H105" s="22"/>
-    </row>
-    <row r="106" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="107" spans="1:11">
-      <c r="A107" s="18" t="s">
+      <c r="B104" s="22"/>
+      <c r="C104" s="22"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22"/>
+      <c r="G104" s="22"/>
+      <c r="H104" s="22"/>
+    </row>
+    <row r="105" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="106" spans="1:11">
+      <c r="A106" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="50.65" customHeight="1">
-      <c r="A108" s="19" t="s">
+    <row r="107" spans="1:11" ht="50.65" customHeight="1">
+      <c r="A107" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B107" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C108" s="19" t="s">
+      <c r="C107" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D108" s="19" t="s">
+      <c r="D107" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E108" s="19" t="s">
+      <c r="E107" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F108" s="19" t="s">
+      <c r="F107" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G108" s="19" t="s">
+      <c r="G107" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H108" s="19" t="s">
+      <c r="H107" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I108" s="19" t="s">
+      <c r="I107" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J108" s="19" t="s">
+      <c r="J107" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K108" s="19" t="s">
+      <c r="K107" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -4826,7 +4841,7 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -4841,7 +4856,7 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -4856,7 +4871,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -4871,7 +4886,7 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
@@ -4884,9 +4899,9 @@
       <c r="J113" s="8"/>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" ht="14.65" thickBot="1">
       <c r="A114" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
@@ -4899,98 +4914,95 @@
       <c r="J114" s="8"/>
       <c r="K114" s="8"/>
     </row>
-    <row r="115" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A115" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-    </row>
-    <row r="116" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A116" s="22" t="s">
+    <row r="115" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A115" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B116" s="22"/>
-      <c r="C116" s="22"/>
-      <c r="D116" s="22"/>
-      <c r="E116" s="22"/>
-      <c r="F116" s="22"/>
-      <c r="G116" s="22"/>
-      <c r="H116" s="22"/>
-      <c r="I116" s="22"/>
-      <c r="J116" s="22"/>
-      <c r="K116" s="22"/>
-    </row>
-    <row r="117" spans="1:11" ht="14.65" thickTop="1">
-      <c r="A117" s="18"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="18"/>
-      <c r="G117" s="18"/>
-      <c r="H117" s="18"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="18"/>
-      <c r="K117" s="18"/>
-    </row>
-    <row r="118" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A118" s="52" t="s">
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="22"/>
+    </row>
+    <row r="116" spans="1:11" ht="14.65" thickTop="1">
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="18"/>
+      <c r="J116" s="18"/>
+      <c r="K116" s="18"/>
+    </row>
+    <row r="117" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A117" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B118" s="52"/>
-      <c r="C118" s="52"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="52"/>
-      <c r="H118" s="52"/>
-      <c r="I118" s="52"/>
-      <c r="J118" s="52"/>
-      <c r="K118" s="52"/>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" s="18" t="s">
+      <c r="B117" s="52"/>
+      <c r="C117" s="52"/>
+      <c r="D117" s="52"/>
+      <c r="E117" s="52"/>
+      <c r="F117" s="52"/>
+      <c r="G117" s="52"/>
+      <c r="H117" s="52"/>
+      <c r="I117" s="52"/>
+      <c r="J117" s="52"/>
+      <c r="K117" s="52"/>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="48" customHeight="1">
-      <c r="A120" s="19" t="s">
+    <row r="119" spans="1:11" ht="48" customHeight="1">
+      <c r="A119" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B120" s="19" t="s">
+      <c r="B119" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C120" s="19" t="s">
+      <c r="C119" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D119" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E120" s="19" t="s">
+      <c r="E119" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F120" s="19" t="s">
+      <c r="F119" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G120" s="19" t="s">
+      <c r="G119" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H120" s="19" t="s">
+      <c r="H119" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -5002,7 +5014,7 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -5014,7 +5026,7 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
@@ -5026,7 +5038,7 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
@@ -5038,7 +5050,7 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -5048,9 +5060,9 @@
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" ht="14.65" thickBot="1">
       <c r="A126" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
@@ -5060,74 +5072,77 @@
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A127" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-    </row>
-    <row r="128" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A128" s="22" t="s">
+    <row r="127" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A127" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-    </row>
-    <row r="129" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="130" spans="1:11">
-      <c r="A130" s="18" t="s">
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+    </row>
+    <row r="128" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="129" spans="1:11">
+      <c r="A129" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="50.65" customHeight="1">
-      <c r="A131" s="19" t="s">
+    <row r="130" spans="1:11" ht="50.65" customHeight="1">
+      <c r="A130" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B130" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C130" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D131" s="19" t="s">
+      <c r="D130" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E131" s="19" t="s">
+      <c r="E130" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F131" s="19" t="s">
+      <c r="F130" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G131" s="19" t="s">
+      <c r="G130" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H131" s="19" t="s">
+      <c r="H130" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I131" s="19" t="s">
+      <c r="I130" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J131" s="19" t="s">
+      <c r="J130" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K131" s="19" t="s">
+      <c r="K130" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -5142,7 +5157,7 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -5157,7 +5172,7 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -5172,7 +5187,7 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -5187,7 +5202,7 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -5200,9 +5215,9 @@
       <c r="J136" s="8"/>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" ht="14.65" thickBot="1">
       <c r="A137" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -5215,87 +5230,80 @@
       <c r="J137" s="8"/>
       <c r="K137" s="8"/>
     </row>
-    <row r="138" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A138" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="8"/>
-      <c r="I138" s="8"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="8"/>
-    </row>
-    <row r="139" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A139" s="22" t="s">
+    <row r="138" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A138" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B139" s="22"/>
-      <c r="C139" s="22"/>
-      <c r="D139" s="22"/>
-      <c r="E139" s="22"/>
-      <c r="F139" s="22"/>
-      <c r="G139" s="22"/>
-      <c r="H139" s="22"/>
-      <c r="I139" s="22"/>
-      <c r="J139" s="22"/>
-      <c r="K139" s="22"/>
-    </row>
-    <row r="140" spans="1:11" ht="14.65" thickTop="1">
-      <c r="A140" s="18"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="18"/>
-    </row>
-    <row r="141" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A141" s="52" t="s">
+      <c r="B138" s="22"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="22"/>
+      <c r="K138" s="22"/>
+    </row>
+    <row r="139" spans="1:11" ht="14.65" thickTop="1">
+      <c r="A139" s="18"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
+      <c r="G139" s="18"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+      <c r="K139" s="18"/>
+    </row>
+    <row r="140" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A140" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="B141" s="52"/>
-      <c r="C141" s="52"/>
-      <c r="D141" s="52"/>
-      <c r="E141" s="52"/>
-      <c r="F141" s="52"/>
-      <c r="G141" s="52"/>
-      <c r="H141" s="52"/>
-      <c r="I141" s="52"/>
-      <c r="J141" s="52"/>
-      <c r="K141" s="52"/>
-    </row>
-    <row r="142" spans="1:11">
-      <c r="A142" s="18" t="s">
+      <c r="B140" s="52"/>
+      <c r="C140" s="52"/>
+      <c r="D140" s="52"/>
+      <c r="E140" s="52"/>
+      <c r="F140" s="52"/>
+      <c r="G140" s="52"/>
+      <c r="H140" s="52"/>
+      <c r="I140" s="52"/>
+      <c r="J140" s="52"/>
+      <c r="K140" s="52"/>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="61.9">
-      <c r="A143" s="19" t="s">
+    <row r="142" spans="1:11" ht="61.9">
+      <c r="A142" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B142" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E143" s="20"/>
-    </row>
-    <row r="144" spans="1:11">
+      <c r="E142" s="20"/>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
@@ -5303,7 +5311,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
@@ -5311,7 +5319,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
@@ -5319,7 +5327,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -5327,61 +5335,61 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
       <c r="D148" s="2"/>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" ht="14.65" thickBot="1">
       <c r="A149" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
       <c r="D149" s="2"/>
     </row>
-    <row r="150" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A150" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="2"/>
-    </row>
-    <row r="151" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A151" s="22" t="s">
+    <row r="150" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A150" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B151" s="22"/>
-      <c r="C151" s="22"/>
-      <c r="D151" s="41" t="s">
+      <c r="B150" s="22"/>
+      <c r="C150" s="22"/>
+      <c r="D150" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="14.65" thickTop="1"/>
-    <row r="153" spans="1:4">
-      <c r="A153" s="18" t="s">
+    <row r="151" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="152" spans="1:4">
+      <c r="A152" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="61.9">
-      <c r="A154" s="19" t="s">
+    <row r="153" spans="1:4" ht="61.9">
+      <c r="A153" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B154" s="19" t="s">
+      <c r="B153" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C153" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="2"/>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -5389,7 +5397,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -5397,7 +5405,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -5405,7 +5413,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -5413,76 +5421,76 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:11" ht="14.65" thickBot="1">
       <c r="A160" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A161" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="2"/>
-    </row>
-    <row r="162" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A162" s="22" t="s">
+    <row r="161" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A161" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B162" s="22"/>
-      <c r="C162" s="22"/>
-      <c r="D162" s="41" t="s">
+      <c r="B161" s="22"/>
+      <c r="C161" s="22"/>
+      <c r="D161" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="164" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A164" s="52" t="s">
+    <row r="162" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="163" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A163" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="B164" s="52"/>
-      <c r="C164" s="52"/>
-      <c r="D164" s="52"/>
-      <c r="E164" s="52"/>
-      <c r="F164" s="52"/>
-      <c r="G164" s="52"/>
-      <c r="H164" s="52"/>
-      <c r="I164" s="52"/>
-      <c r="J164" s="52"/>
-      <c r="K164" s="52"/>
-    </row>
-    <row r="165" spans="1:11">
-      <c r="A165" s="18" t="s">
+      <c r="B163" s="52"/>
+      <c r="C163" s="52"/>
+      <c r="D163" s="52"/>
+      <c r="E163" s="52"/>
+      <c r="F163" s="52"/>
+      <c r="G163" s="52"/>
+      <c r="H163" s="52"/>
+      <c r="I163" s="52"/>
+      <c r="J163" s="52"/>
+      <c r="K163" s="52"/>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="61.9">
-      <c r="A166" s="19" t="s">
+    <row r="165" spans="1:11" ht="61.9">
+      <c r="A165" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B166" s="19" t="s">
+      <c r="B165" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="D165" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B166" s="8"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="2"/>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
@@ -5490,7 +5498,7 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
@@ -5498,7 +5506,7 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
@@ -5506,7 +5514,7 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
@@ -5514,61 +5522,61 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="2"/>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" ht="14.65" thickBot="1">
       <c r="A172" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="2"/>
     </row>
-    <row r="173" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A173" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="2"/>
-    </row>
-    <row r="174" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A174" s="22" t="s">
+    <row r="173" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A173" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B174" s="22"/>
-      <c r="C174" s="22"/>
-      <c r="D174" s="41" t="s">
+      <c r="B173" s="22"/>
+      <c r="C173" s="22"/>
+      <c r="D173" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="176" spans="1:11">
-      <c r="A176" s="18" t="s">
+    <row r="174" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="175" spans="1:11">
+      <c r="A175" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="61.9">
-      <c r="A177" s="19" t="s">
+    <row r="176" spans="1:11" ht="61.9">
+      <c r="A176" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B177" s="19" t="s">
+      <c r="B176" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="C176" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="8"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="2"/>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -5576,7 +5584,7 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
@@ -5584,7 +5592,7 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
@@ -5592,7 +5600,7 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -5600,76 +5608,76 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="2"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" ht="14.65" thickBot="1">
       <c r="A183" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="2"/>
     </row>
-    <row r="184" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A184" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="2"/>
-    </row>
-    <row r="185" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A185" s="22" t="s">
+    <row r="184" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A184" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B185" s="22"/>
-      <c r="C185" s="22"/>
-      <c r="D185" s="41" t="s">
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="187" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A187" s="52" t="s">
+    <row r="185" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="186" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A186" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="B187" s="52"/>
-      <c r="C187" s="52"/>
-      <c r="D187" s="52"/>
-      <c r="E187" s="52"/>
-      <c r="F187" s="52"/>
-      <c r="G187" s="52"/>
-      <c r="H187" s="52"/>
-      <c r="I187" s="52"/>
-      <c r="J187" s="52"/>
-      <c r="K187" s="52"/>
-    </row>
-    <row r="188" spans="1:11">
-      <c r="A188" s="18" t="s">
+      <c r="B186" s="52"/>
+      <c r="C186" s="52"/>
+      <c r="D186" s="52"/>
+      <c r="E186" s="52"/>
+      <c r="F186" s="52"/>
+      <c r="G186" s="52"/>
+      <c r="H186" s="52"/>
+      <c r="I186" s="52"/>
+      <c r="J186" s="52"/>
+      <c r="K186" s="52"/>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="61.9">
-      <c r="A189" s="19" t="s">
+    <row r="188" spans="1:11" ht="61.9">
+      <c r="A188" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B189" s="19" t="s">
+      <c r="B188" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C188" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="2"/>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -5677,15 +5685,15 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="2"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:4">
       <c r="A192" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -5693,7 +5701,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -5701,61 +5709,61 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="2"/>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" ht="14.65" thickBot="1">
       <c r="A195" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="2"/>
     </row>
-    <row r="196" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A196" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="2"/>
-    </row>
-    <row r="197" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A197" s="22" t="s">
+    <row r="196" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A196" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B197" s="22"/>
-      <c r="C197" s="22"/>
-      <c r="D197" s="41" t="s">
+      <c r="B196" s="22"/>
+      <c r="C196" s="22"/>
+      <c r="D196" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="14.65" thickTop="1"/>
-    <row r="199" spans="1:4">
-      <c r="A199" s="18" t="s">
+    <row r="197" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="198" spans="1:4">
+      <c r="A198" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="61.9">
-      <c r="A200" s="19" t="s">
+    <row r="199" spans="1:4" ht="61.9">
+      <c r="A199" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B200" s="19" t="s">
+      <c r="B199" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="C199" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="2"/>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -5763,7 +5771,7 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -5771,7 +5779,7 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -5779,7 +5787,7 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -5787,76 +5795,84 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
       <c r="D205" s="2"/>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" ht="14.65" thickBot="1">
       <c r="A206" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
       <c r="D206" s="2"/>
     </row>
-    <row r="207" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A207" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="2"/>
-    </row>
-    <row r="208" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A208" s="22" t="s">
+    <row r="207" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A207" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B208" s="22"/>
-      <c r="C208" s="22"/>
-      <c r="D208" s="41" t="s">
+      <c r="B207" s="22"/>
+      <c r="C207" s="22"/>
+      <c r="D207" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="210" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A210" s="52" t="s">
+    <row r="208" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="209" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A209" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B210" s="52"/>
-      <c r="C210" s="52"/>
-      <c r="D210" s="52"/>
-      <c r="E210" s="52"/>
-      <c r="F210" s="52"/>
-      <c r="G210" s="52"/>
-      <c r="H210" s="52"/>
-      <c r="I210" s="52"/>
-      <c r="J210" s="52"/>
-      <c r="K210" s="52"/>
+      <c r="B209" s="52"/>
+      <c r="C209" s="52"/>
+      <c r="D209" s="52"/>
+      <c r="E209" s="52"/>
+      <c r="F209" s="52"/>
+      <c r="G209" s="52"/>
+      <c r="H209" s="52"/>
+      <c r="I209" s="52"/>
+      <c r="J209" s="52"/>
+      <c r="K209" s="52"/>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" ht="61.9">
+      <c r="A211" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B211" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="212" spans="1:11">
-      <c r="A212" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" ht="61.9">
-      <c r="A213" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B213" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A212" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="2"/>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="2"/>
     </row>
     <row r="214" spans="1:11">
       <c r="A214" s="8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -5864,7 +5880,7 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -5872,7 +5888,7 @@
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -5880,69 +5896,69 @@
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
       <c r="D217" s="2"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" ht="14.65" thickBot="1">
       <c r="A218" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
       <c r="D218" s="2"/>
     </row>
-    <row r="219" spans="1:11">
-      <c r="A219" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="2"/>
-    </row>
-    <row r="220" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A220" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="2"/>
-    </row>
-    <row r="221" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A221" s="22" t="s">
+    <row r="219" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A219" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B221" s="22"/>
-      <c r="C221" s="22"/>
-      <c r="D221" s="41" t="s">
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="220" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="221" spans="1:11">
+      <c r="A221" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" ht="61.9">
+      <c r="A222" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B222" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
     <row r="223" spans="1:11">
-      <c r="A223" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" ht="61.9">
-      <c r="A224" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B224" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A223" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="2"/>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="2"/>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -5950,7 +5966,7 @@
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -5958,7 +5974,7 @@
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -5966,170 +5982,178 @@
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
       <c r="D228" s="2"/>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" ht="14.65" thickBot="1">
       <c r="A229" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
       <c r="D229" s="2"/>
     </row>
-    <row r="230" spans="1:11">
-      <c r="A230" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B230" s="8"/>
-      <c r="C230" s="8"/>
-      <c r="D230" s="2"/>
-    </row>
-    <row r="231" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A231" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
-      <c r="D231" s="2"/>
-    </row>
-    <row r="232" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A232" s="22" t="s">
+    <row r="230" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A230" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B232" s="22"/>
-      <c r="C232" s="22"/>
-      <c r="D232" s="41" t="s">
+      <c r="B230" s="22"/>
+      <c r="C230" s="22"/>
+      <c r="D230" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="234" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A234" s="52" t="s">
+    <row r="231" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="232" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A232" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B234" s="52"/>
-      <c r="C234" s="52"/>
-      <c r="D234" s="52"/>
-      <c r="E234" s="52"/>
-      <c r="F234" s="52"/>
-      <c r="G234" s="52"/>
-      <c r="H234" s="52"/>
-      <c r="I234" s="52"/>
-      <c r="J234" s="52"/>
-      <c r="K234" s="52"/>
+      <c r="B232" s="52"/>
+      <c r="C232" s="52"/>
+      <c r="D232" s="52"/>
+      <c r="E232" s="52"/>
+      <c r="F232" s="52"/>
+      <c r="G232" s="52"/>
+      <c r="H232" s="52"/>
+      <c r="I232" s="52"/>
+      <c r="J232" s="52"/>
+      <c r="K232" s="52"/>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" ht="61.9">
+      <c r="A234" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B234" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="2"/>
     </row>
     <row r="236" spans="1:11">
-      <c r="A236" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" ht="61.9">
-      <c r="A237" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B237" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11">
+      <c r="A236" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="2"/>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="2"/>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" s="8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
       <c r="D238" s="2"/>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:4">
       <c r="A239" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
       <c r="D239" s="2"/>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:4">
       <c r="A240" s="8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
       <c r="D240" s="2"/>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" ht="14.65" thickBot="1">
       <c r="A241" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
       <c r="D241" s="2"/>
     </row>
-    <row r="242" spans="1:4">
-      <c r="A242" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B242" s="8"/>
-      <c r="C242" s="8"/>
-      <c r="D242" s="2"/>
-    </row>
-    <row r="243" spans="1:4">
-      <c r="A243" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B243" s="8"/>
-      <c r="C243" s="8"/>
-      <c r="D243" s="2"/>
-    </row>
-    <row r="244" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A244" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B244" s="8"/>
-      <c r="C244" s="8"/>
-      <c r="D244" s="2"/>
-    </row>
-    <row r="245" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A245" s="22" t="s">
+    <row r="242" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A242" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B245" s="22"/>
-      <c r="C245" s="22"/>
-      <c r="D245" s="41" t="s">
+      <c r="B242" s="22"/>
+      <c r="C242" s="22"/>
+      <c r="D242" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="243" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="244" spans="1:4">
+      <c r="A244" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="61.9">
+      <c r="A245" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B245" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="2"/>
+    </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" ht="61.9">
-      <c r="A248" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B248" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A247" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="2"/>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="2"/>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -6137,7 +6161,7 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -6145,92 +6169,100 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
       <c r="D251" s="2"/>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" ht="14.65" thickBot="1">
       <c r="A252" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
       <c r="D252" s="2"/>
     </row>
-    <row r="253" spans="1:4">
-      <c r="A253" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B253" s="8"/>
-      <c r="C253" s="8"/>
-      <c r="D253" s="2"/>
-    </row>
-    <row r="254" spans="1:4">
-      <c r="A254" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
-      <c r="D254" s="2"/>
-    </row>
-    <row r="255" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A255" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B255" s="8"/>
-      <c r="C255" s="8"/>
-      <c r="D255" s="2"/>
-    </row>
-    <row r="256" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A256" s="22" t="s">
+    <row r="253" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A253" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B256" s="22"/>
-      <c r="C256" s="22"/>
-      <c r="D256" s="41" t="s">
+      <c r="B253" s="22"/>
+      <c r="C253" s="22"/>
+      <c r="D253" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="258" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A258" s="52" t="s">
+    <row r="254" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="255" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A255" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B258" s="52"/>
-      <c r="C258" s="52"/>
-      <c r="D258" s="52"/>
-      <c r="E258" s="52"/>
-      <c r="F258" s="52"/>
-      <c r="G258" s="52"/>
-      <c r="H258" s="52"/>
-      <c r="I258" s="52"/>
-      <c r="J258" s="52"/>
-      <c r="K258" s="52"/>
+      <c r="B255" s="52"/>
+      <c r="C255" s="52"/>
+      <c r="D255" s="52"/>
+      <c r="E255" s="52"/>
+      <c r="F255" s="52"/>
+      <c r="G255" s="52"/>
+      <c r="H255" s="52"/>
+      <c r="I255" s="52"/>
+      <c r="J255" s="52"/>
+      <c r="K255" s="52"/>
+    </row>
+    <row r="256" spans="1:11">
+      <c r="A256" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" ht="61.9">
+      <c r="A257" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B257" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11">
+      <c r="A258" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B258" s="8"/>
+      <c r="C258" s="8"/>
+      <c r="D258" s="2"/>
+    </row>
+    <row r="259" spans="1:11">
+      <c r="A259" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" s="8"/>
+      <c r="C259" s="8"/>
+      <c r="D259" s="2"/>
     </row>
     <row r="260" spans="1:11">
-      <c r="A260" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11" ht="61.9">
-      <c r="A261" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B261" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A260" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B260" s="8"/>
+      <c r="C260" s="8"/>
+      <c r="D260" s="2"/>
+    </row>
+    <row r="261" spans="1:11">
+      <c r="A261" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B261" s="8"/>
+      <c r="C261" s="8"/>
+      <c r="D261" s="2"/>
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B262" s="8"/>
       <c r="C262" s="8"/>
@@ -6238,85 +6270,85 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B263" s="8"/>
       <c r="C263" s="8"/>
       <c r="D263" s="2"/>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" ht="14.65" thickBot="1">
       <c r="A264" s="8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
       <c r="D264" s="2"/>
     </row>
-    <row r="265" spans="1:11">
-      <c r="A265" s="8" t="s">
+    <row r="265" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A265" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B265" s="22"/>
+      <c r="C265" s="22"/>
+      <c r="D265" s="41" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="267" spans="1:11">
+      <c r="A267" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" ht="61.9">
+      <c r="A268" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B268" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B269" s="8"/>
+      <c r="C269" s="8"/>
+      <c r="D269" s="2"/>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
+      <c r="D270" s="2"/>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
+      <c r="D271" s="2"/>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B265" s="8"/>
-      <c r="C265" s="8"/>
-      <c r="D265" s="2"/>
-    </row>
-    <row r="266" spans="1:11">
-      <c r="A266" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B266" s="8"/>
-      <c r="C266" s="8"/>
-      <c r="D266" s="2"/>
-    </row>
-    <row r="267" spans="1:11">
-      <c r="A267" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B267" s="8"/>
-      <c r="C267" s="8"/>
-      <c r="D267" s="2"/>
-    </row>
-    <row r="268" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A268" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B268" s="8"/>
-      <c r="C268" s="8"/>
-      <c r="D268" s="2"/>
-    </row>
-    <row r="269" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A269" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B269" s="22"/>
-      <c r="C269" s="22"/>
-      <c r="D269" s="41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="271" spans="1:11">
-      <c r="A271" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="272" spans="1:11" ht="61.9">
-      <c r="A272" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B272" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="B272" s="8"/>
+      <c r="C272" s="8"/>
+      <c r="D272" s="2"/>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -6324,78 +6356,46 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
       <c r="D274" s="2"/>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:4" ht="14.65" thickBot="1">
       <c r="A275" s="8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
       <c r="D275" s="2"/>
     </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B276" s="8"/>
-      <c r="C276" s="8"/>
-      <c r="D276" s="2"/>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B277" s="8"/>
-      <c r="C277" s="8"/>
-      <c r="D277" s="2"/>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B278" s="8"/>
-      <c r="C278" s="8"/>
-      <c r="D278" s="2"/>
-    </row>
-    <row r="279" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A279" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
-      <c r="D279" s="2"/>
-    </row>
-    <row r="280" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A280" s="22" t="s">
+    <row r="276" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A276" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B280" s="22"/>
-      <c r="C280" s="22"/>
-      <c r="D280" s="41" t="s">
+      <c r="B276" s="22"/>
+      <c r="C276" s="22"/>
+      <c r="D276" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="277" spans="1:4" ht="14.65" thickTop="1"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A141:K141"/>
-    <mergeCell ref="A118:K118"/>
-    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="A117:K117"/>
+    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A72:K72"/>
-    <mergeCell ref="A258:K258"/>
-    <mergeCell ref="A234:K234"/>
-    <mergeCell ref="A164:K164"/>
-    <mergeCell ref="A187:K187"/>
-    <mergeCell ref="A210:K210"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A255:K255"/>
+    <mergeCell ref="A232:K232"/>
+    <mergeCell ref="A163:K163"/>
+    <mergeCell ref="A186:K186"/>
+    <mergeCell ref="A209:K209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6404,7 +6404,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C4150F-376A-437D-894C-F649880C6D47}">
-  <dimension ref="A1:K281"/>
+  <dimension ref="A1:K277"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="17" customWidth="1"/>
@@ -7052,40 +7052,52 @@
       <c r="J48" s="52"/>
       <c r="K48" s="52"/>
     </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="18" t="s">
+    <row r="49" spans="1:11">
+      <c r="A49" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="51.4" customHeight="1">
-      <c r="A51" s="19" t="s">
+    <row r="50" spans="1:11" ht="51.4" customHeight="1">
+      <c r="A50" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B50" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C50" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D50" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E50" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F50" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G51" s="19" t="s">
+      <c r="G50" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H51" s="19" t="s">
+      <c r="H50" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -7097,7 +7109,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -7109,7 +7121,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -7121,7 +7133,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -7133,7 +7145,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -7143,9 +7155,9 @@
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" ht="14.65" thickBot="1">
       <c r="A57" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -7155,74 +7167,77 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A58" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-    </row>
-    <row r="59" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A59" s="22" t="s">
+    <row r="58" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A58" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-    </row>
-    <row r="60" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="61" spans="1:11">
-      <c r="A61" s="18" t="s">
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+    </row>
+    <row r="59" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="60" spans="1:11">
+      <c r="A60" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="49.15" customHeight="1">
-      <c r="A62" s="19" t="s">
+    <row r="61" spans="1:11" ht="49.15" customHeight="1">
+      <c r="A61" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B61" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C61" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D61" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E61" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F61" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="G61" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="H61" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="19" t="s">
+      <c r="I61" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J62" s="19" t="s">
+      <c r="J61" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K62" s="19" t="s">
+      <c r="K61" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -7237,7 +7252,7 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -7252,7 +7267,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -7267,7 +7282,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -7282,7 +7297,7 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -7295,9 +7310,9 @@
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
     </row>
-    <row r="68" spans="1:11">
-      <c r="A68" s="8" t="s">
-        <v>14</v>
+    <row r="68" spans="1:11" ht="14.65" thickBot="1">
+      <c r="A68" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -7310,98 +7325,95 @@
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A69" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-    </row>
-    <row r="70" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A70" s="22" t="s">
+    <row r="69" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A69" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-    </row>
-    <row r="71" spans="1:11" s="34" customFormat="1" ht="14.65" thickTop="1">
-      <c r="A71" s="18"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-    </row>
-    <row r="72" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A72" s="52" t="s">
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+    </row>
+    <row r="70" spans="1:11" s="34" customFormat="1" ht="14.65" thickTop="1">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+    </row>
+    <row r="71" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A71" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="52"/>
-      <c r="K72" s="52"/>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="18" t="s">
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="48" customHeight="1">
-      <c r="A74" s="19" t="s">
+    <row r="73" spans="1:11" ht="48" customHeight="1">
+      <c r="A73" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B73" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C73" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D73" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E73" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F74" s="19" t="s">
+      <c r="F73" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G74" s="19" t="s">
+      <c r="G73" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H74" s="19" t="s">
+      <c r="H73" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -7413,7 +7425,7 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -7425,7 +7437,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -7437,7 +7449,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -7449,7 +7461,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -7459,9 +7471,9 @@
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" ht="14.65" thickBot="1">
       <c r="A80" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -7471,74 +7483,77 @@
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
     </row>
-    <row r="81" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A81" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-    </row>
-    <row r="82" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A82" s="22" t="s">
+    <row r="81" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A81" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="22"/>
-    </row>
-    <row r="83" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="84" spans="1:11">
-      <c r="A84" s="18" t="s">
+      <c r="B81" s="22"/>
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+    </row>
+    <row r="82" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="83" spans="1:11">
+      <c r="A83" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="50.65" customHeight="1">
-      <c r="A85" s="19" t="s">
+    <row r="84" spans="1:11" ht="50.65" customHeight="1">
+      <c r="A84" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B84" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C84" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D85" s="19" t="s">
+      <c r="D84" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E85" s="19" t="s">
+      <c r="E84" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F85" s="19" t="s">
+      <c r="F84" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G85" s="19" t="s">
+      <c r="G84" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H85" s="19" t="s">
+      <c r="H84" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I85" s="19" t="s">
+      <c r="I84" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J85" s="19" t="s">
+      <c r="J84" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K85" s="19" t="s">
+      <c r="K84" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -7553,7 +7568,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -7568,7 +7583,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -7583,7 +7598,7 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -7598,7 +7613,7 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -7611,9 +7626,9 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
     </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="8" t="s">
-        <v>14</v>
+    <row r="91" spans="1:11" ht="14.65" thickBot="1">
+      <c r="A91" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -7626,98 +7641,95 @@
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A92" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-    </row>
-    <row r="93" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A93" s="22" t="s">
+    <row r="92" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A92" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B93" s="22"/>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22"/>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="22"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="22"/>
-    </row>
-    <row r="94" spans="1:11" ht="14.65" thickTop="1">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="18"/>
-      <c r="F94" s="18"/>
-      <c r="G94" s="18"/>
-      <c r="H94" s="18"/>
-      <c r="I94" s="18"/>
-      <c r="J94" s="18"/>
-      <c r="K94" s="18"/>
-    </row>
-    <row r="95" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A95" s="52" t="s">
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="22"/>
+      <c r="K92" s="22"/>
+    </row>
+    <row r="93" spans="1:11" ht="14.65" thickTop="1">
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="18"/>
+    </row>
+    <row r="94" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A94" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="18" t="s">
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="52"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="48" customHeight="1">
-      <c r="A97" s="19" t="s">
+    <row r="96" spans="1:11" ht="48" customHeight="1">
+      <c r="A96" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B97" s="19" t="s">
+      <c r="B96" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C96" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D97" s="19" t="s">
+      <c r="D96" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E96" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F97" s="19" t="s">
+      <c r="F96" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G97" s="19" t="s">
+      <c r="G96" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H97" s="19" t="s">
+      <c r="H96" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -7729,7 +7741,7 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -7741,7 +7753,7 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -7753,7 +7765,7 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -7765,7 +7777,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -7775,9 +7787,9 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" ht="14.65" thickBot="1">
       <c r="A103" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -7787,74 +7799,77 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A104" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-    </row>
-    <row r="105" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A105" s="22" t="s">
+    <row r="104" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A104" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B105" s="22"/>
-      <c r="C105" s="22"/>
-      <c r="D105" s="22"/>
-      <c r="E105" s="22"/>
-      <c r="F105" s="22"/>
-      <c r="G105" s="22"/>
-      <c r="H105" s="22"/>
-    </row>
-    <row r="106" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="107" spans="1:11">
-      <c r="A107" s="18" t="s">
+      <c r="B104" s="22"/>
+      <c r="C104" s="22"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22"/>
+      <c r="G104" s="22"/>
+      <c r="H104" s="22"/>
+    </row>
+    <row r="105" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="106" spans="1:11">
+      <c r="A106" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="50.65" customHeight="1">
-      <c r="A108" s="19" t="s">
+    <row r="107" spans="1:11" ht="50.65" customHeight="1">
+      <c r="A107" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B107" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C108" s="19" t="s">
+      <c r="C107" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D108" s="19" t="s">
+      <c r="D107" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E108" s="19" t="s">
+      <c r="E107" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F108" s="19" t="s">
+      <c r="F107" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G108" s="19" t="s">
+      <c r="G107" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H108" s="19" t="s">
+      <c r="H107" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I108" s="19" t="s">
+      <c r="I107" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J108" s="19" t="s">
+      <c r="J107" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K108" s="19" t="s">
+      <c r="K107" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -7869,7 +7884,7 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -7884,7 +7899,7 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -7899,7 +7914,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -7914,7 +7929,7 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
@@ -7927,9 +7942,9 @@
       <c r="J113" s="8"/>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11">
-      <c r="A114" s="8" t="s">
-        <v>14</v>
+    <row r="114" spans="1:11" ht="14.65" thickBot="1">
+      <c r="A114" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
@@ -7942,98 +7957,95 @@
       <c r="J114" s="8"/>
       <c r="K114" s="8"/>
     </row>
-    <row r="115" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A115" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-    </row>
-    <row r="116" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A116" s="22" t="s">
+    <row r="115" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A115" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B116" s="22"/>
-      <c r="C116" s="22"/>
-      <c r="D116" s="22"/>
-      <c r="E116" s="22"/>
-      <c r="F116" s="22"/>
-      <c r="G116" s="22"/>
-      <c r="H116" s="22"/>
-      <c r="I116" s="22"/>
-      <c r="J116" s="22"/>
-      <c r="K116" s="22"/>
-    </row>
-    <row r="117" spans="1:11" ht="14.65" thickTop="1">
-      <c r="A117" s="18"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="18"/>
-      <c r="G117" s="18"/>
-      <c r="H117" s="18"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="18"/>
-      <c r="K117" s="18"/>
-    </row>
-    <row r="118" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A118" s="52" t="s">
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="22"/>
+    </row>
+    <row r="116" spans="1:11" ht="14.65" thickTop="1">
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="18"/>
+      <c r="J116" s="18"/>
+      <c r="K116" s="18"/>
+    </row>
+    <row r="117" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A117" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B118" s="52"/>
-      <c r="C118" s="52"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="52"/>
-      <c r="H118" s="52"/>
-      <c r="I118" s="52"/>
-      <c r="J118" s="52"/>
-      <c r="K118" s="52"/>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" s="18" t="s">
+      <c r="B117" s="52"/>
+      <c r="C117" s="52"/>
+      <c r="D117" s="52"/>
+      <c r="E117" s="52"/>
+      <c r="F117" s="52"/>
+      <c r="G117" s="52"/>
+      <c r="H117" s="52"/>
+      <c r="I117" s="52"/>
+      <c r="J117" s="52"/>
+      <c r="K117" s="52"/>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="48" customHeight="1">
-      <c r="A120" s="19" t="s">
+    <row r="119" spans="1:11" ht="48" customHeight="1">
+      <c r="A119" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B120" s="19" t="s">
+      <c r="B119" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C120" s="19" t="s">
+      <c r="C119" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D119" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E120" s="19" t="s">
+      <c r="E119" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F120" s="19" t="s">
+      <c r="F119" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G120" s="19" t="s">
+      <c r="G119" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H120" s="19" t="s">
+      <c r="H119" s="19" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -8045,7 +8057,7 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -8057,7 +8069,7 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
@@ -8069,7 +8081,7 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
@@ -8081,7 +8093,7 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -8091,9 +8103,9 @@
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" ht="14.65" thickBot="1">
       <c r="A126" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
@@ -8103,74 +8115,77 @@
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A127" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-    </row>
-    <row r="128" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A128" s="22" t="s">
+    <row r="127" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A127" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-    </row>
-    <row r="129" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="130" spans="1:11">
-      <c r="A130" s="18" t="s">
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+    </row>
+    <row r="128" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="129" spans="1:11">
+      <c r="A129" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="50.65" customHeight="1">
-      <c r="A131" s="19" t="s">
+    <row r="130" spans="1:11" ht="50.65" customHeight="1">
+      <c r="A130" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B130" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C130" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D131" s="19" t="s">
+      <c r="D130" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E131" s="19" t="s">
+      <c r="E130" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F131" s="19" t="s">
+      <c r="F130" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G131" s="19" t="s">
+      <c r="G130" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H131" s="19" t="s">
+      <c r="H130" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I131" s="19" t="s">
+      <c r="I130" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J131" s="19" t="s">
+      <c r="J130" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K131" s="19" t="s">
+      <c r="K130" s="19" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -8185,7 +8200,7 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -8200,7 +8215,7 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -8215,7 +8230,7 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -8230,7 +8245,7 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -8243,9 +8258,9 @@
       <c r="J136" s="8"/>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11">
-      <c r="A137" s="8" t="s">
-        <v>14</v>
+    <row r="137" spans="1:11" ht="14.65" thickBot="1">
+      <c r="A137" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -8258,87 +8273,80 @@
       <c r="J137" s="8"/>
       <c r="K137" s="8"/>
     </row>
-    <row r="138" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A138" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="8"/>
-      <c r="I138" s="8"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="8"/>
-    </row>
-    <row r="139" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A139" s="22" t="s">
+    <row r="138" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A138" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B139" s="22"/>
-      <c r="C139" s="22"/>
-      <c r="D139" s="22"/>
-      <c r="E139" s="22"/>
-      <c r="F139" s="22"/>
-      <c r="G139" s="22"/>
-      <c r="H139" s="22"/>
-      <c r="I139" s="22"/>
-      <c r="J139" s="22"/>
-      <c r="K139" s="22"/>
-    </row>
-    <row r="140" spans="1:11" ht="14.65" thickTop="1">
-      <c r="A140" s="18"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="18"/>
-    </row>
-    <row r="141" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A141" s="52" t="s">
+      <c r="B138" s="22"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="22"/>
+      <c r="K138" s="22"/>
+    </row>
+    <row r="139" spans="1:11" ht="14.65" thickTop="1">
+      <c r="A139" s="18"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
+      <c r="G139" s="18"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+      <c r="K139" s="18"/>
+    </row>
+    <row r="140" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A140" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="B141" s="52"/>
-      <c r="C141" s="52"/>
-      <c r="D141" s="52"/>
-      <c r="E141" s="52"/>
-      <c r="F141" s="52"/>
-      <c r="G141" s="52"/>
-      <c r="H141" s="52"/>
-      <c r="I141" s="52"/>
-      <c r="J141" s="52"/>
-      <c r="K141" s="52"/>
-    </row>
-    <row r="142" spans="1:11">
-      <c r="A142" s="18" t="s">
+      <c r="B140" s="52"/>
+      <c r="C140" s="52"/>
+      <c r="D140" s="52"/>
+      <c r="E140" s="52"/>
+      <c r="F140" s="52"/>
+      <c r="G140" s="52"/>
+      <c r="H140" s="52"/>
+      <c r="I140" s="52"/>
+      <c r="J140" s="52"/>
+      <c r="K140" s="52"/>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="61.9">
-      <c r="A143" s="19" t="s">
+    <row r="142" spans="1:11" ht="61.9">
+      <c r="A142" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B142" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E143" s="20"/>
-    </row>
-    <row r="144" spans="1:11">
+      <c r="E142" s="20"/>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
@@ -8346,7 +8354,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
@@ -8354,7 +8362,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
@@ -8362,7 +8370,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -8370,61 +8378,61 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
       <c r="D148" s="2"/>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" ht="14.65" thickBot="1">
       <c r="A149" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
       <c r="D149" s="2"/>
     </row>
-    <row r="150" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A150" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="2"/>
-    </row>
-    <row r="151" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A151" s="22" t="s">
+    <row r="150" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A150" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B151" s="22"/>
-      <c r="C151" s="22"/>
-      <c r="D151" s="36" t="s">
+      <c r="B150" s="22"/>
+      <c r="C150" s="22"/>
+      <c r="D150" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="14.65" thickTop="1"/>
-    <row r="153" spans="1:4">
-      <c r="A153" s="18" t="s">
+    <row r="151" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="152" spans="1:4">
+      <c r="A152" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="61.9">
-      <c r="A154" s="19" t="s">
+    <row r="153" spans="1:4" ht="61.9">
+      <c r="A153" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B154" s="19" t="s">
+      <c r="B153" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C153" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="2"/>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -8432,7 +8440,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -8440,7 +8448,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -8448,7 +8456,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -8456,76 +8464,76 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:11" ht="14.65" thickBot="1">
       <c r="A160" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A161" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="2"/>
-    </row>
-    <row r="162" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A162" s="22" t="s">
+    <row r="161" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A161" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B162" s="22"/>
-      <c r="C162" s="22"/>
-      <c r="D162" s="36" t="s">
+      <c r="B161" s="22"/>
+      <c r="C161" s="22"/>
+      <c r="D161" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="164" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A164" s="52" t="s">
+    <row r="162" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="163" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A163" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="B164" s="52"/>
-      <c r="C164" s="52"/>
-      <c r="D164" s="52"/>
-      <c r="E164" s="52"/>
-      <c r="F164" s="52"/>
-      <c r="G164" s="52"/>
-      <c r="H164" s="52"/>
-      <c r="I164" s="52"/>
-      <c r="J164" s="52"/>
-      <c r="K164" s="52"/>
-    </row>
-    <row r="165" spans="1:11">
-      <c r="A165" s="18" t="s">
+      <c r="B163" s="52"/>
+      <c r="C163" s="52"/>
+      <c r="D163" s="52"/>
+      <c r="E163" s="52"/>
+      <c r="F163" s="52"/>
+      <c r="G163" s="52"/>
+      <c r="H163" s="52"/>
+      <c r="I163" s="52"/>
+      <c r="J163" s="52"/>
+      <c r="K163" s="52"/>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="61.9">
-      <c r="A166" s="19" t="s">
+    <row r="165" spans="1:11" ht="61.9">
+      <c r="A165" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B166" s="19" t="s">
+      <c r="B165" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="D165" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B166" s="8"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="2"/>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
@@ -8533,7 +8541,7 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
@@ -8541,7 +8549,7 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
@@ -8549,7 +8557,7 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
@@ -8557,61 +8565,61 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="2"/>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" ht="14.65" thickBot="1">
       <c r="A172" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="2"/>
     </row>
-    <row r="173" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A173" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="2"/>
-    </row>
-    <row r="174" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A174" s="22" t="s">
+    <row r="173" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A173" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B174" s="22"/>
-      <c r="C174" s="22"/>
-      <c r="D174" s="36" t="s">
+      <c r="B173" s="22"/>
+      <c r="C173" s="22"/>
+      <c r="D173" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="176" spans="1:11">
-      <c r="A176" s="18" t="s">
+    <row r="174" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="175" spans="1:11">
+      <c r="A175" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="61.9">
-      <c r="A177" s="19" t="s">
+    <row r="176" spans="1:11" ht="61.9">
+      <c r="A176" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B177" s="19" t="s">
+      <c r="B176" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="C176" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="8"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="2"/>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -8619,7 +8627,7 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
@@ -8627,7 +8635,7 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
@@ -8635,7 +8643,7 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -8643,76 +8651,76 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="2"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" ht="14.65" thickBot="1">
       <c r="A183" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="2"/>
     </row>
-    <row r="184" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A184" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="2"/>
-    </row>
-    <row r="185" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A185" s="22" t="s">
+    <row r="184" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A184" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B185" s="22"/>
-      <c r="C185" s="22"/>
-      <c r="D185" s="36" t="s">
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="187" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A187" s="52" t="s">
+    <row r="185" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="186" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A186" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="B187" s="52"/>
-      <c r="C187" s="52"/>
-      <c r="D187" s="52"/>
-      <c r="E187" s="52"/>
-      <c r="F187" s="52"/>
-      <c r="G187" s="52"/>
-      <c r="H187" s="52"/>
-      <c r="I187" s="52"/>
-      <c r="J187" s="52"/>
-      <c r="K187" s="52"/>
-    </row>
-    <row r="188" spans="1:11">
-      <c r="A188" s="18" t="s">
+      <c r="B186" s="52"/>
+      <c r="C186" s="52"/>
+      <c r="D186" s="52"/>
+      <c r="E186" s="52"/>
+      <c r="F186" s="52"/>
+      <c r="G186" s="52"/>
+      <c r="H186" s="52"/>
+      <c r="I186" s="52"/>
+      <c r="J186" s="52"/>
+      <c r="K186" s="52"/>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="61.9">
-      <c r="A189" s="19" t="s">
+    <row r="188" spans="1:11" ht="61.9">
+      <c r="A188" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B189" s="19" t="s">
+      <c r="B188" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C188" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="2"/>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -8720,15 +8728,15 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="2"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:4">
       <c r="A192" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -8736,7 +8744,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -8744,61 +8752,61 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="2"/>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" ht="14.65" thickBot="1">
       <c r="A195" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="2"/>
     </row>
-    <row r="196" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A196" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="2"/>
-    </row>
-    <row r="197" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A197" s="22" t="s">
+    <row r="196" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A196" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B197" s="22"/>
-      <c r="C197" s="22"/>
-      <c r="D197" s="36" t="s">
+      <c r="B196" s="22"/>
+      <c r="C196" s="22"/>
+      <c r="D196" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="14.65" thickTop="1"/>
-    <row r="199" spans="1:4">
-      <c r="A199" s="18" t="s">
+    <row r="197" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="198" spans="1:4">
+      <c r="A198" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="61.9">
-      <c r="A200" s="19" t="s">
+    <row r="199" spans="1:4" ht="61.9">
+      <c r="A199" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B200" s="19" t="s">
+      <c r="B199" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="C199" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="2"/>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -8806,7 +8814,7 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -8814,7 +8822,7 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -8822,7 +8830,7 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -8830,76 +8838,84 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
       <c r="D205" s="2"/>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" ht="14.65" thickBot="1">
       <c r="A206" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
       <c r="D206" s="2"/>
     </row>
-    <row r="207" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A207" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="2"/>
-    </row>
-    <row r="208" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A208" s="22" t="s">
+    <row r="207" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A207" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B208" s="22"/>
-      <c r="C208" s="22"/>
-      <c r="D208" s="36" t="s">
+      <c r="B207" s="22"/>
+      <c r="C207" s="22"/>
+      <c r="D207" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="210" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A210" s="52" t="s">
+    <row r="208" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="209" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A209" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B210" s="52"/>
-      <c r="C210" s="52"/>
-      <c r="D210" s="52"/>
-      <c r="E210" s="52"/>
-      <c r="F210" s="52"/>
-      <c r="G210" s="52"/>
-      <c r="H210" s="52"/>
-      <c r="I210" s="52"/>
-      <c r="J210" s="52"/>
-      <c r="K210" s="52"/>
+      <c r="B209" s="52"/>
+      <c r="C209" s="52"/>
+      <c r="D209" s="52"/>
+      <c r="E209" s="52"/>
+      <c r="F209" s="52"/>
+      <c r="G209" s="52"/>
+      <c r="H209" s="52"/>
+      <c r="I209" s="52"/>
+      <c r="J209" s="52"/>
+      <c r="K209" s="52"/>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" ht="61.9">
+      <c r="A211" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B211" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="212" spans="1:11">
-      <c r="A212" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" ht="61.9">
-      <c r="A213" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B213" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A212" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="2"/>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="2"/>
     </row>
     <row r="214" spans="1:11">
       <c r="A214" s="8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -8907,7 +8923,7 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -8915,7 +8931,7 @@
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -8923,69 +8939,69 @@
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
       <c r="D217" s="2"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" ht="14.65" thickBot="1">
       <c r="A218" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
       <c r="D218" s="2"/>
     </row>
-    <row r="219" spans="1:11">
-      <c r="A219" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="2"/>
-    </row>
-    <row r="220" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A220" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="2"/>
-    </row>
-    <row r="221" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A221" s="22" t="s">
+    <row r="219" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A219" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B221" s="22"/>
-      <c r="C221" s="22"/>
-      <c r="D221" s="36" t="s">
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="220" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="221" spans="1:11">
+      <c r="A221" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" ht="61.9">
+      <c r="A222" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B222" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
     <row r="223" spans="1:11">
-      <c r="A223" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" ht="61.9">
-      <c r="A224" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B224" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A223" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="2"/>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="2"/>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -8993,7 +9009,7 @@
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -9001,7 +9017,7 @@
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -9009,170 +9025,178 @@
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
       <c r="D228" s="2"/>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" ht="14.65" thickBot="1">
       <c r="A229" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
       <c r="D229" s="2"/>
     </row>
-    <row r="230" spans="1:11">
-      <c r="A230" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B230" s="8"/>
-      <c r="C230" s="8"/>
-      <c r="D230" s="2"/>
-    </row>
-    <row r="231" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A231" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
-      <c r="D231" s="2"/>
-    </row>
-    <row r="232" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A232" s="22" t="s">
+    <row r="230" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A230" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B232" s="22"/>
-      <c r="C232" s="22"/>
-      <c r="D232" s="36" t="s">
+      <c r="B230" s="22"/>
+      <c r="C230" s="22"/>
+      <c r="D230" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="234" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A234" s="52" t="s">
+    <row r="231" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="232" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A232" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B234" s="52"/>
-      <c r="C234" s="52"/>
-      <c r="D234" s="52"/>
-      <c r="E234" s="52"/>
-      <c r="F234" s="52"/>
-      <c r="G234" s="52"/>
-      <c r="H234" s="52"/>
-      <c r="I234" s="52"/>
-      <c r="J234" s="52"/>
-      <c r="K234" s="52"/>
+      <c r="B232" s="52"/>
+      <c r="C232" s="52"/>
+      <c r="D232" s="52"/>
+      <c r="E232" s="52"/>
+      <c r="F232" s="52"/>
+      <c r="G232" s="52"/>
+      <c r="H232" s="52"/>
+      <c r="I232" s="52"/>
+      <c r="J232" s="52"/>
+      <c r="K232" s="52"/>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" ht="61.9">
+      <c r="A234" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B234" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="2"/>
     </row>
     <row r="236" spans="1:11">
-      <c r="A236" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" ht="61.9">
-      <c r="A237" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B237" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11">
+      <c r="A236" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="2"/>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="2"/>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" s="8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
       <c r="D238" s="2"/>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:4">
       <c r="A239" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
       <c r="D239" s="2"/>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:4">
       <c r="A240" s="8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
       <c r="D240" s="2"/>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" ht="14.65" thickBot="1">
       <c r="A241" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
       <c r="D241" s="2"/>
     </row>
-    <row r="242" spans="1:4">
-      <c r="A242" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B242" s="8"/>
-      <c r="C242" s="8"/>
-      <c r="D242" s="2"/>
-    </row>
-    <row r="243" spans="1:4">
-      <c r="A243" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B243" s="8"/>
-      <c r="C243" s="8"/>
-      <c r="D243" s="2"/>
-    </row>
-    <row r="244" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A244" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B244" s="8"/>
-      <c r="C244" s="8"/>
-      <c r="D244" s="2"/>
-    </row>
-    <row r="245" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A245" s="22" t="s">
+    <row r="242" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A242" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B245" s="22"/>
-      <c r="C245" s="22"/>
-      <c r="D245" s="36" t="s">
+      <c r="B242" s="22"/>
+      <c r="C242" s="22"/>
+      <c r="D242" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="243" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="244" spans="1:4">
+      <c r="A244" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="61.9">
+      <c r="A245" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B245" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="2"/>
+    </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" ht="61.9">
-      <c r="A248" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B248" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A247" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="2"/>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="2"/>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -9180,7 +9204,7 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -9188,92 +9212,100 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
       <c r="D251" s="2"/>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" ht="14.65" thickBot="1">
       <c r="A252" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
       <c r="D252" s="2"/>
     </row>
-    <row r="253" spans="1:4">
-      <c r="A253" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B253" s="8"/>
-      <c r="C253" s="8"/>
-      <c r="D253" s="2"/>
-    </row>
-    <row r="254" spans="1:4">
-      <c r="A254" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
-      <c r="D254" s="2"/>
-    </row>
-    <row r="255" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A255" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B255" s="8"/>
-      <c r="C255" s="8"/>
-      <c r="D255" s="2"/>
-    </row>
-    <row r="256" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A256" s="22" t="s">
+    <row r="253" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A253" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B256" s="22"/>
-      <c r="C256" s="22"/>
-      <c r="D256" s="36" t="s">
+      <c r="B253" s="22"/>
+      <c r="C253" s="22"/>
+      <c r="D253" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="258" spans="1:11" s="34" customFormat="1" ht="15.6">
-      <c r="A258" s="52" t="s">
+    <row r="254" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="255" spans="1:11" s="34" customFormat="1" ht="15.6">
+      <c r="A255" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B258" s="52"/>
-      <c r="C258" s="52"/>
-      <c r="D258" s="52"/>
-      <c r="E258" s="52"/>
-      <c r="F258" s="52"/>
-      <c r="G258" s="52"/>
-      <c r="H258" s="52"/>
-      <c r="I258" s="52"/>
-      <c r="J258" s="52"/>
-      <c r="K258" s="52"/>
+      <c r="B255" s="52"/>
+      <c r="C255" s="52"/>
+      <c r="D255" s="52"/>
+      <c r="E255" s="52"/>
+      <c r="F255" s="52"/>
+      <c r="G255" s="52"/>
+      <c r="H255" s="52"/>
+      <c r="I255" s="52"/>
+      <c r="J255" s="52"/>
+      <c r="K255" s="52"/>
+    </row>
+    <row r="256" spans="1:11">
+      <c r="A256" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" ht="61.9">
+      <c r="A257" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B257" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11">
+      <c r="A258" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B258" s="8"/>
+      <c r="C258" s="8"/>
+      <c r="D258" s="2"/>
+    </row>
+    <row r="259" spans="1:11">
+      <c r="A259" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" s="8"/>
+      <c r="C259" s="8"/>
+      <c r="D259" s="2"/>
     </row>
     <row r="260" spans="1:11">
-      <c r="A260" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11" ht="61.9">
-      <c r="A261" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B261" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A260" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B260" s="8"/>
+      <c r="C260" s="8"/>
+      <c r="D260" s="2"/>
+    </row>
+    <row r="261" spans="1:11">
+      <c r="A261" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B261" s="8"/>
+      <c r="C261" s="8"/>
+      <c r="D261" s="2"/>
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B262" s="8"/>
       <c r="C262" s="8"/>
@@ -9281,85 +9313,85 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B263" s="8"/>
       <c r="C263" s="8"/>
       <c r="D263" s="2"/>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" ht="14.65" thickBot="1">
       <c r="A264" s="8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
       <c r="D264" s="2"/>
     </row>
-    <row r="265" spans="1:11">
-      <c r="A265" s="8" t="s">
+    <row r="265" spans="1:11" ht="15" thickTop="1" thickBot="1">
+      <c r="A265" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B265" s="22"/>
+      <c r="C265" s="22"/>
+      <c r="D265" s="36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" ht="14.65" thickTop="1"/>
+    <row r="267" spans="1:11">
+      <c r="A267" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" ht="61.9">
+      <c r="A268" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B268" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B269" s="8"/>
+      <c r="C269" s="8"/>
+      <c r="D269" s="2"/>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
+      <c r="D270" s="2"/>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
+      <c r="D271" s="2"/>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B265" s="8"/>
-      <c r="C265" s="8"/>
-      <c r="D265" s="2"/>
-    </row>
-    <row r="266" spans="1:11">
-      <c r="A266" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B266" s="8"/>
-      <c r="C266" s="8"/>
-      <c r="D266" s="2"/>
-    </row>
-    <row r="267" spans="1:11">
-      <c r="A267" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B267" s="8"/>
-      <c r="C267" s="8"/>
-      <c r="D267" s="2"/>
-    </row>
-    <row r="268" spans="1:11" ht="14.65" thickBot="1">
-      <c r="A268" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B268" s="8"/>
-      <c r="C268" s="8"/>
-      <c r="D268" s="2"/>
-    </row>
-    <row r="269" spans="1:11" ht="15" thickTop="1" thickBot="1">
-      <c r="A269" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B269" s="22"/>
-      <c r="C269" s="22"/>
-      <c r="D269" s="36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11" ht="14.65" thickTop="1"/>
-    <row r="271" spans="1:11">
-      <c r="A271" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="272" spans="1:11" ht="61.9">
-      <c r="A272" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B272" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="B272" s="8"/>
+      <c r="C272" s="8"/>
+      <c r="D272" s="2"/>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -9367,78 +9399,46 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
       <c r="D274" s="2"/>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:4" ht="14.65" thickBot="1">
       <c r="A275" s="8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
       <c r="D275" s="2"/>
     </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B276" s="8"/>
-      <c r="C276" s="8"/>
-      <c r="D276" s="2"/>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B277" s="8"/>
-      <c r="C277" s="8"/>
-      <c r="D277" s="2"/>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B278" s="8"/>
-      <c r="C278" s="8"/>
-      <c r="D278" s="2"/>
-    </row>
-    <row r="279" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A279" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
-      <c r="D279" s="2"/>
-    </row>
-    <row r="280" spans="1:4" ht="15" thickTop="1" thickBot="1">
-      <c r="A280" s="22" t="s">
+    <row r="276" spans="1:4" ht="15" thickTop="1" thickBot="1">
+      <c r="A276" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B280" s="22"/>
-      <c r="C280" s="22"/>
-      <c r="D280" s="36" t="s">
+      <c r="B276" s="22"/>
+      <c r="C276" s="22"/>
+      <c r="D276" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="14.65" thickTop="1"/>
+    <row r="277" spans="1:4" ht="14.65" thickTop="1"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A72:K72"/>
-    <mergeCell ref="A258:K258"/>
-    <mergeCell ref="A118:K118"/>
-    <mergeCell ref="A141:K141"/>
-    <mergeCell ref="A164:K164"/>
-    <mergeCell ref="A187:K187"/>
-    <mergeCell ref="A210:K210"/>
-    <mergeCell ref="A234:K234"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A255:K255"/>
+    <mergeCell ref="A117:K117"/>
+    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="A163:K163"/>
+    <mergeCell ref="A186:K186"/>
+    <mergeCell ref="A209:K209"/>
+    <mergeCell ref="A232:K232"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
